--- a/dataset/Faulty/uninit_memory_access.xlsx
+++ b/dataset/Faulty/uninit_memory_access.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,19 +583,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>#define MAX 10 #define ERROR 0x1 typedef struct { int arr[MAX]; int a; int b; int c; } uninit_memory_access_007_s_001; long ** uninit_memory_access_009_doubleptr_gbl; volatile uninit_memory_access_010_s_001 *uninit_memory_access_010_s_001_arr_gbl; enum {max_buffer = 24}; typedef enum { true=1, false=0} bool; extern volatile int vflag; void uninit_memory_access_007 () { uninit_memory_access_007_s_001 st; uninit_memory_access_007_func_001(&amp;st); uninit_memory_access_007_func_002(&amp;st); uninit_memory_access_007_func_003(&amp;st); uninit_memory_access_007_func_004(st.a); } void uninit_memory_access_007_func_001(uninit_memory_access_007_s_001* st) { memset(st-&gt;arr, 0, 1); st-&gt;a = 1; } void uninit_memory_access_007_func_002(uninit_memory_access_007_s_001 *st) { int temp=0; int i; for (i = 0; i &lt; MAX; i++) { temp += st-&gt;arr[i];/*Tool should detect this line as error*/ /*ERROR:Uninitialized Memory Access*/ } } void uninit_memory_access_007_func_004(int num) { int temp; if(num != 0) { temp = num; } } void uninit_memory_access_007_func_003(uninit_memory_access_007_s_001 *st) { st-&gt;b = 10; st-&gt;c =20; }</t>
+          <t>#define MAX 10 #define ERROR 0x1 typedef struct { int arr[MAX]; int a; int b; int c; } uninit_memory_access_007_s_001; long ** uninit_memory_access_009_doubleptr_gbl; volatile uninit_memory_access_010_s_001 *uninit_memory_access_010_s_001_arr_gbl; enum {max_buffer = 24}; typedef enum { true=1, false=0} bool; extern volatile int vflag; void uninit_memory_access_007 () { uninit_memory_access_007_s_001 st; uninit_memory_access_007_func_001(&amp;st); uninit_memory_access_007_func_002(&amp;st); uninit_memory_access_007_func_003(&amp;st); uninit_memory_access_007_func_004(st.a); } void uninit_memory_access_007_func_003(uninit_memory_access_007_s_001 *st) { st-&gt;b = 10; st-&gt;c =20; } void uninit_memory_access_007_func_002(uninit_memory_access_007_s_001 *st) { int temp=0; int i; for (i = 0; i &lt; MAX; i++) { temp += st-&gt;arr[i];/*Tool should detect this line as error*/ /*ERROR:Uninitialized Memory Access*/ } } void uninit_memory_access_007_func_004(int num) { int temp; if(num != 0) { temp = num; } } void uninit_memory_access_007_func_001(uninit_memory_access_007_s_001* st) { memset(st-&gt;arr, 0, 1); st-&gt;a = 1; }</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,14 +610,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>#define ERROR 0x1 long ** uninit_memory_access_009_doubleptr_gbl; volatile uninit_memory_access_010_s_001 *uninit_memory_access_010_s_001_arr_gbl; enum {max_buffer = 24}; typedef enum { true=1, false=0} bool; extern volatile int vflag; void uninit_memory_access_009() { int flag=0,i,j; if(uninit_memory_access_009_func_001(flag)==0) { uninit_memory_access_009_func_002(); } if(uninit_memory_access_009_func_001(flag)==0) { for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { uninit_memory_access_009_doubleptr_gbl[i][j] += 1;/*Tool should detect this line as error*/ /*ERROR:Uninitialized Memory Access*/ } free (uninit_memory_access_009_doubleptr_gbl[i]); uninit_memory_access_009_doubleptr_gbl[i] = NULL; } free(uninit_memory_access_009_doubleptr_gbl); uninit_memory_access_009_doubleptr_gbl = NULL; } } void uninit_memory_access_009_func_002() { int i,j; uninit_memory_access_009_doubleptr_gbl=(long**) malloc(10*sizeof(long*)); for(i=0;i&lt;10;i++) { uninit_memory_access_009_doubleptr_gbl[i]=(long*) malloc(10*sizeof(long)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { ;/*uninit_memory_access_009_doubleptr_gbl[i][j]=i;*/ } } } int uninit_memory_access_009_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
+          <t>#define ERROR 0x1 long ** uninit_memory_access_009_doubleptr_gbl; volatile uninit_memory_access_010_s_001 *uninit_memory_access_010_s_001_arr_gbl; enum {max_buffer = 24}; typedef enum { true=1, false=0} bool; extern volatile int vflag; void uninit_memory_access_009() { int flag=0,i,j; if(uninit_memory_access_009_func_001(flag)==0) { uninit_memory_access_009_func_002(); } if(uninit_memory_access_009_func_001(flag)==0) { for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { uninit_memory_access_009_doubleptr_gbl[i][j] += 1;/*Tool should detect this line as error*/ /*ERROR:Uninitialized Memory Access*/ } free (uninit_memory_access_009_doubleptr_gbl[i]); uninit_memory_access_009_doubleptr_gbl[i] = NULL; } free(uninit_memory_access_009_doubleptr_gbl); uninit_memory_access_009_doubleptr_gbl = NULL; } } int uninit_memory_access_009_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; } void uninit_memory_access_009_func_002() { int i,j; uninit_memory_access_009_doubleptr_gbl=(long**) malloc(10*sizeof(long*)); for(i=0;i&lt;10;i++) { uninit_memory_access_009_doubleptr_gbl[i]=(long*) malloc(10*sizeof(long)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { ;/*uninit_memory_access_009_doubleptr_gbl[i][j]=i;*/ } } }</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -676,14 +676,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/uninit_memory_access.c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
